--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008432213998538026</v>
       </c>
       <c r="C2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>36088271</v>
+        <v>4098056</v>
       </c>
       <c r="L2" t="n">
-        <v>19744671</v>
+        <v>1953200</v>
       </c>
       <c r="M2" t="n">
-        <v>4586393</v>
+        <v>417776</v>
       </c>
       <c r="N2" t="n">
-        <v>167980</v>
+        <v>12581</v>
       </c>
       <c r="O2" t="n">
-        <v>2742325</v>
+        <v>256720</v>
       </c>
       <c r="P2" t="n">
-        <v>1072330</v>
+        <v>105733</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998533725738525</v>
+        <v>0.9998550415039062</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8663302659988403</v>
+        <v>0.7802667021751404</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7513797879219055</v>
+        <v>0.601084291934967</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6820374727249146</v>
+        <v>0.4952616691589355</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2043358385562897</v>
+        <v>0.119277186691761</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7282118797302246</v>
+        <v>0.5575693845748901</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8231671452522278</v>
+        <v>0.6706095933914185</v>
       </c>
       <c r="X2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>38712019</v>
+        <v>4813274</v>
       </c>
       <c r="AG2" t="n">
-        <v>23936510</v>
+        <v>3010697</v>
       </c>
       <c r="AH2" t="n">
-        <v>6414507</v>
+        <v>804213</v>
       </c>
       <c r="AI2" t="n">
-        <v>473159</v>
+        <v>59267</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3676427</v>
+        <v>460431</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563227891921997</v>
+        <v>0.9555724859237671</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114070534706116</v>
+        <v>0.9118132591247559</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580120801925659</v>
+        <v>0.8582125902175903</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619145274162292</v>
+        <v>0.6612037420272827</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019697904586792</v>
+        <v>0.9019888043403625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002020802637879015</v>
       </c>
       <c r="C3" t="n">
-        <v>5568</v>
+        <v>700</v>
       </c>
       <c r="D3" t="n">
-        <v>36088271</v>
+        <v>4098056</v>
       </c>
       <c r="E3" t="n">
-        <v>4214433</v>
+        <v>887422</v>
       </c>
       <c r="F3" t="n">
-        <v>102587</v>
+        <v>35040</v>
       </c>
       <c r="G3" t="n">
-        <v>9770</v>
+        <v>2924</v>
       </c>
       <c r="H3" t="n">
-        <v>6651</v>
+        <v>2719</v>
       </c>
       <c r="I3" t="n">
-        <v>367</v>
+        <v>178</v>
       </c>
       <c r="J3" t="n">
-        <v>80549514</v>
+        <v>10068700</v>
       </c>
       <c r="K3" t="n">
-        <v>85332141</v>
+        <v>10234895</v>
       </c>
       <c r="L3" t="n">
-        <v>98488646</v>
+        <v>11810232</v>
       </c>
       <c r="M3" t="n">
-        <v>121707531</v>
+        <v>15051453</v>
       </c>
       <c r="N3" t="n">
-        <v>129958409</v>
+        <v>16233330</v>
       </c>
       <c r="O3" t="n">
-        <v>126226249</v>
+        <v>15701360</v>
       </c>
       <c r="P3" t="n">
-        <v>129550520</v>
+        <v>16170476</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8926631808280945</v>
+        <v>0.8152027726173401</v>
       </c>
       <c r="S3" t="n">
-        <v>0.750572681427002</v>
+        <v>0.5901785492897034</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6129644513130188</v>
+        <v>0.4450215399265289</v>
       </c>
       <c r="U3" t="n">
-        <v>0.234775185585022</v>
+        <v>0.1401408016681671</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6724281907081604</v>
+        <v>0.5024533271789551</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6931127309799194</v>
+        <v>0.5461697578430176</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38712019</v>
+        <v>4813274</v>
       </c>
       <c r="Z3" t="n">
-        <v>1591784</v>
+        <v>198388</v>
       </c>
       <c r="AA3" t="n">
-        <v>68580</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>54698</v>
+        <v>6867</v>
       </c>
       <c r="AC3" t="n">
-        <v>326</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80556960</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>89132297</v>
+        <v>11165177</v>
       </c>
       <c r="AG3" t="n">
-        <v>102695121</v>
+        <v>12815311</v>
       </c>
       <c r="AH3" t="n">
-        <v>122784182</v>
+        <v>15344357</v>
       </c>
       <c r="AI3" t="n">
-        <v>130370832</v>
+        <v>16295858</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126850187</v>
+        <v>15855036</v>
       </c>
       <c r="AK3" t="n">
-        <v>129674836</v>
+        <v>16209148</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575629830360413</v>
+        <v>0.9574769735336304</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099209904670715</v>
+        <v>0.9097115993499756</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572890758514404</v>
+        <v>0.8566603064537048</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613048911094666</v>
+        <v>0.6601800322532654</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014734625816345</v>
+        <v>0.9011573195457458</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03191057304788653</v>
       </c>
       <c r="C4" t="n">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="D4" t="n">
-        <v>5214273</v>
+        <v>1069323</v>
       </c>
       <c r="E4" t="n">
-        <v>19744671</v>
+        <v>1953200</v>
       </c>
       <c r="F4" t="n">
-        <v>1171775</v>
+        <v>233595</v>
       </c>
       <c r="G4" t="n">
-        <v>59189</v>
+        <v>16034</v>
       </c>
       <c r="H4" t="n">
-        <v>105314</v>
+        <v>33262</v>
       </c>
       <c r="I4" t="n">
-        <v>10459</v>
+        <v>4016</v>
       </c>
       <c r="J4" t="n">
-        <v>7446</v>
+        <v>920</v>
       </c>
       <c r="K4" t="n">
-        <v>5568212</v>
+        <v>1154066</v>
       </c>
       <c r="L4" t="n">
-        <v>6533213</v>
+        <v>1296261</v>
       </c>
       <c r="M4" t="n">
-        <v>2138154</v>
+        <v>425770</v>
       </c>
       <c r="N4" t="n">
-        <v>654098</v>
+        <v>92896</v>
       </c>
       <c r="O4" t="n">
-        <v>1023509</v>
+        <v>203707</v>
       </c>
       <c r="P4" t="n">
-        <v>230358</v>
+        <v>51934</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999266862869263</v>
+        <v>0.9999275207519531</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8792996406555176</v>
+        <v>0.7973521947860718</v>
       </c>
       <c r="S4" t="n">
-        <v>0.750976026058197</v>
+        <v>0.5955815315246582</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6456587910652161</v>
+        <v>0.4687994122505188</v>
       </c>
       <c r="U4" t="n">
-        <v>0.218500480055809</v>
+        <v>0.1288700252771378</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6992092132568359</v>
+        <v>0.5285784602165222</v>
       </c>
       <c r="W4" t="n">
-        <v>0.752562403678894</v>
+        <v>0.6020264625549316</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1650806</v>
+        <v>208961</v>
       </c>
       <c r="Z4" t="n">
-        <v>23936510</v>
+        <v>3010697</v>
       </c>
       <c r="AA4" t="n">
-        <v>664902</v>
+        <v>83070</v>
       </c>
       <c r="AB4" t="n">
-        <v>44224</v>
+        <v>5580</v>
       </c>
       <c r="AC4" t="n">
-        <v>9155</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1768056</v>
+        <v>223784</v>
       </c>
       <c r="AG4" t="n">
-        <v>2326738</v>
+        <v>291182</v>
       </c>
       <c r="AH4" t="n">
-        <v>1061503</v>
+        <v>132866</v>
       </c>
       <c r="AI4" t="n">
-        <v>241675</v>
+        <v>30368</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399571</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569424390792847</v>
+        <v>0.9565237760543823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663366317749</v>
+        <v>0.9107611775398254</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576504588127136</v>
+        <v>0.8574357628822327</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616095304489136</v>
+        <v>0.660691499710083</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017215967178345</v>
+        <v>0.9015728235244751</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>242094</v>
+        <v>61987</v>
       </c>
       <c r="E5" t="n">
-        <v>1968507</v>
+        <v>326156</v>
       </c>
       <c r="F5" t="n">
-        <v>4586393</v>
+        <v>417776</v>
       </c>
       <c r="G5" t="n">
-        <v>219078</v>
+        <v>30361</v>
       </c>
       <c r="H5" t="n">
-        <v>423406</v>
+        <v>89812</v>
       </c>
       <c r="I5" t="n">
-        <v>42714</v>
+        <v>12665</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4339376</v>
+        <v>928983</v>
       </c>
       <c r="L5" t="n">
-        <v>6561470</v>
+        <v>1356307</v>
       </c>
       <c r="M5" t="n">
-        <v>2895922</v>
+        <v>521001</v>
       </c>
       <c r="N5" t="n">
-        <v>547513</v>
+        <v>77193</v>
       </c>
       <c r="O5" t="n">
-        <v>1335917</v>
+        <v>254213</v>
       </c>
       <c r="P5" t="n">
-        <v>474792</v>
+        <v>87857</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999433159828186</v>
+        <v>0.9999439716339111</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9245584607124329</v>
+        <v>0.8731086254119873</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9002902507781982</v>
+        <v>0.8384156823158264</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9616678953170776</v>
+        <v>0.9423263072967529</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9908503293991089</v>
+        <v>0.9896388053894043</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9820340871810913</v>
+        <v>0.9721052646636963</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9946306347846985</v>
+        <v>0.9914844632148743</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64693</v>
+        <v>8176</v>
       </c>
       <c r="Z5" t="n">
-        <v>684803</v>
+        <v>86508</v>
       </c>
       <c r="AA5" t="n">
-        <v>6414507</v>
+        <v>804213</v>
       </c>
       <c r="AB5" t="n">
-        <v>79806</v>
+        <v>10008</v>
       </c>
       <c r="AC5" t="n">
-        <v>233442</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1715628</v>
+        <v>213765</v>
       </c>
       <c r="AG5" t="n">
-        <v>2369631</v>
+        <v>298810</v>
       </c>
       <c r="AH5" t="n">
-        <v>1067808</v>
+        <v>134564</v>
       </c>
       <c r="AI5" t="n">
-        <v>242334</v>
+        <v>30507</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401815</v>
+        <v>50502</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734734296798706</v>
+        <v>0.9733461737632751</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642394185066223</v>
+        <v>0.9640599489212036</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837862849235535</v>
+        <v>0.9837091565132141</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996314525604248</v>
+        <v>0.9962917566299438</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938978552818298</v>
+        <v>0.9938759207725525</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998382568359375</v>
+        <v>0.9983792304992676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>351</v>
+        <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>101443</v>
+        <v>17344</v>
       </c>
       <c r="E6" t="n">
-        <v>159663</v>
+        <v>22596</v>
       </c>
       <c r="F6" t="n">
-        <v>198215</v>
+        <v>24534</v>
       </c>
       <c r="G6" t="n">
-        <v>167980</v>
+        <v>12581</v>
       </c>
       <c r="H6" t="n">
-        <v>81085</v>
+        <v>11065</v>
       </c>
       <c r="I6" t="n">
-        <v>6756</v>
+        <v>1610</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>52110</v>
+        <v>6591</v>
       </c>
       <c r="Z6" t="n">
-        <v>43017</v>
+        <v>5395</v>
       </c>
       <c r="AA6" t="n">
-        <v>87434</v>
+        <v>11026</v>
       </c>
       <c r="AB6" t="n">
-        <v>473159</v>
+        <v>59267</v>
       </c>
       <c r="AC6" t="n">
-        <v>55925</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>10062</v>
+        <v>5313</v>
       </c>
       <c r="E7" t="n">
-        <v>177406</v>
+        <v>54852</v>
       </c>
       <c r="F7" t="n">
-        <v>630623</v>
+        <v>121459</v>
       </c>
       <c r="G7" t="n">
-        <v>347614</v>
+        <v>39109</v>
       </c>
       <c r="H7" t="n">
-        <v>2742325</v>
+        <v>256720</v>
       </c>
       <c r="I7" t="n">
-        <v>170062</v>
+        <v>33465</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>6486</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237939</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60821</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3676427</v>
+        <v>460431</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>794</v>
+        <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>99</v>
       </c>
       <c r="E8" t="n">
-        <v>13204</v>
+        <v>5235</v>
       </c>
       <c r="F8" t="n">
-        <v>34954</v>
+        <v>11142</v>
       </c>
       <c r="G8" t="n">
-        <v>18447</v>
+        <v>4468</v>
       </c>
       <c r="H8" t="n">
-        <v>407053</v>
+        <v>66849</v>
       </c>
       <c r="I8" t="n">
-        <v>1072330</v>
+        <v>105733</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
